--- a/diseases/d196/2020-2025.xlsx
+++ b/diseases/d196/2020-2025.xlsx
@@ -2545,11 +2545,11 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01049867293433623</v>
+        <v>0.0103132587174378</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01145309774654862</v>
+        <v>0.01125082769175033</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3137,11 +3137,11 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.008589823309911463</v>
+        <v>0.008438120768812746</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3433,11 +3433,11 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009544248122123847</v>
+        <v>0.009375689743125274</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3729,11 +3729,11 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01097588534044242</v>
+        <v>0.01078204320459407</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4025,11 +4025,11 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.008589823309911463</v>
+        <v>0.008438120768812746</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4321,11 +4321,11 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.01383915977707958</v>
+        <v>0.01359475012753165</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4617,11 +4617,11 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.03817699248849539</v>
+        <v>0.0375027589725011</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4913,11 +4913,11 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.04438075376787588</v>
+        <v>0.04359695730553253</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5209,11 +5209,11 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.03769978008238919</v>
+        <v>0.03703397448534483</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5505,11 +5505,11 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.03579093045796443</v>
+        <v>0.03515883653671978</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5801,11 +5801,11 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0310188063969025</v>
+        <v>0.03047099166515714</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -9649,11 +9649,11 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.04764183000504954</v>
+        <v>0.04751068696454927</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9945,11 +9945,11 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.04669842743069212</v>
+        <v>0.04656988128208294</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10241,11 +10241,11 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.04386821970761987</v>
+        <v>0.04374746423468398</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10537,11 +10537,11 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03820780426147537</v>
+        <v>0.03810263013988605</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10833,11 +10833,11 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.04056631069736891</v>
+        <v>0.04045464434605185</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11129,11 +11129,11 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.04433992099479858</v>
+        <v>0.04421786707591714</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11425,11 +11425,11 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.06415137505630433</v>
+        <v>0.0639747864077099</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11721,11 +11721,11 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.08349112783063137</v>
+        <v>0.08326130289826951</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12017,11 +12017,11 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.07783071238448687</v>
+        <v>0.07761646880347157</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12313,11 +12313,11 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0.05801925832298113</v>
+        <v>0.05785954947167881</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12609,11 +12609,11 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.04103801198454762</v>
+        <v>0.04092504718728501</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12905,11 +12905,11 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.04198141455890503</v>
+        <v>0.04186585286975134</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">

--- a/diseases/d196/2020-2025.xlsx
+++ b/diseases/d196/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14834,6 +15309,11 @@
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">

--- a/diseases/d196/2020-2025.xlsx
+++ b/diseases/d196/2020-2025.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.2670143014862483</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.06675357537156208</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.05340286029724966</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.0801042904458745</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>1.415175797877116</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.4005214522293725</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.1735592959660614</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.04005214522293725</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.3337678768578104</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.1335071507431242</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.1335071507431242</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.1335071507431242</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.0103132587174378</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0.08016458858898501</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0.01125082769175033</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0.1068861181186467</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0.008438120768812746</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0.3473798838856016</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0.009375689743125274</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0.09352535335381583</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0.01078204320459407</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0.09352535335381583</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0.008438120768812746</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0.240493765766955</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>0.01359475012753165</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0.3607406486504325</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0.0375027589725011</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0.1336076476483083</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5055,11 +4635,6 @@
       <c r="R30" t="n">
         <v>0.04359695730553253</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5072,22 +4647,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5208,11 +4773,6 @@
       <c r="R31" t="n">
         <v>0.2538545305317858</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4785,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5361,11 +4911,6 @@
       <c r="R32" t="n">
         <v>0.03703397448534483</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5378,22 +4923,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5514,11 +5049,6 @@
       <c r="R33" t="n">
         <v>0.6279559439470491</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5531,22 +5061,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5667,11 +5187,6 @@
       <c r="R34" t="n">
         <v>0.03515883653671978</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,22 +5199,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5820,11 +5325,6 @@
       <c r="R35" t="n">
         <v>0.2939368248262783</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5837,22 +5337,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5973,11 +5463,6 @@
       <c r="R36" t="n">
         <v>0.03047099166515714</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5990,22 +5475,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6126,11 +5601,6 @@
       <c r="R37" t="n">
         <v>0.1068861181186467</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,22 +5613,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6279,11 +5739,6 @@
       <c r="R38" t="n">
         <v>0.0669710276637224</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6296,22 +5751,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6432,11 +5877,6 @@
       <c r="R39" t="n">
         <v>0.02678841106548896</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5889,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6585,11 +6015,6 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,22 +6027,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6738,11 +6153,6 @@
       <c r="R41" t="n">
         <v>0.04018261659823344</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6755,22 +6165,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6891,11 +6291,6 @@
       <c r="R42" t="n">
         <v>0.1875188774584227</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6908,22 +6303,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7044,11 +6429,6 @@
       <c r="R43" t="n">
         <v>0.1473362608601893</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7061,22 +6441,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7197,11 +6567,6 @@
       <c r="R44" t="n">
         <v>0.2277014940566562</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7214,22 +6579,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7350,11 +6705,6 @@
       <c r="R45" t="n">
         <v>0.2009130829911672</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7367,22 +6717,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7503,11 +6843,6 @@
       <c r="R46" t="n">
         <v>0.1741246719256782</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7520,22 +6855,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7656,11 +6981,6 @@
       <c r="R47" t="n">
         <v>0.2277014940566562</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7673,22 +6993,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7809,11 +7119,6 @@
       <c r="R48" t="n">
         <v>0.1875188774584227</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7826,22 +7131,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7962,11 +7257,6 @@
       <c r="R49" t="n">
         <v>0.2946725217203786</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7979,22 +7269,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8115,11 +7395,6 @@
       <c r="R50" t="n">
         <v>0.5374368788783208</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8132,22 +7407,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8268,11 +7533,6 @@
       <c r="R51" t="n">
         <v>0.631488332682027</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8285,22 +7545,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8421,11 +7671,6 @@
       <c r="R52" t="n">
         <v>0.2821543614111184</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8438,22 +7683,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8574,11 +7809,6 @@
       <c r="R53" t="n">
         <v>0.1209232977476222</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8591,22 +7821,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8727,11 +7947,6 @@
       <c r="R54" t="n">
         <v>0.1209232977476222</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8744,22 +7959,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8880,11 +8085,6 @@
       <c r="R55" t="n">
         <v>0.3627698932428666</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8897,22 +8097,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9033,11 +8223,6 @@
       <c r="R56" t="n">
         <v>0.1881029076074123</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9050,22 +8235,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9186,11 +8361,6 @@
       <c r="R57" t="n">
         <v>0.3090262053550345</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9203,22 +8373,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9339,11 +8499,6 @@
       <c r="R58" t="n">
         <v>0.1209232977476222</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9356,22 +8511,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9492,11 +8637,6 @@
       <c r="R59" t="n">
         <v>0.1343592197195802</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9509,22 +8649,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9645,11 +8775,6 @@
       <c r="R60" t="n">
         <v>0.1746669856354543</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9662,22 +8787,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9798,11 +8913,6 @@
       <c r="R61" t="n">
         <v>0.1477951416915382</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9815,22 +8925,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9951,11 +9051,6 @@
       <c r="R62" t="n">
         <v>0.04751068696454927</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9968,22 +9063,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10104,11 +9189,6 @@
       <c r="R63" t="n">
         <v>0.1888087777740241</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10121,22 +9201,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10257,11 +9327,6 @@
       <c r="R64" t="n">
         <v>0.04656988128208294</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10274,22 +9339,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10410,11 +9465,6 @@
       <c r="R65" t="n">
         <v>0.3506448730089018</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10427,22 +9477,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10563,11 +9603,6 @@
       <c r="R66" t="n">
         <v>0.04374746423468398</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10580,22 +9615,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10716,11 +9741,6 @@
       <c r="R67" t="n">
         <v>0.2022951190435972</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10733,22 +9753,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10869,11 +9879,6 @@
       <c r="R68" t="n">
         <v>0.03810263013988605</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10886,22 +9891,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11022,11 +10017,6 @@
       <c r="R69" t="n">
         <v>0.06743170634786574</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11039,22 +10029,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11175,11 +10155,6 @@
       <c r="R70" t="n">
         <v>0.04045464434605185</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11192,22 +10167,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11328,11 +10293,6 @@
       <c r="R71" t="n">
         <v>0.2022951190435972</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11345,22 +10305,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11481,11 +10431,6 @@
       <c r="R72" t="n">
         <v>0.04421786707591714</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11498,22 +10443,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11634,11 +10569,6 @@
       <c r="R73" t="n">
         <v>0.7147760872873768</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11651,22 +10581,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11787,11 +10707,6 @@
       <c r="R74" t="n">
         <v>0.0639747864077099</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11804,22 +10719,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11940,11 +10845,6 @@
       <c r="R75" t="n">
         <v>0.1348634126957315</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11957,22 +10857,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12093,11 +10983,6 @@
       <c r="R76" t="n">
         <v>0.08326130289826951</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12110,22 +10995,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12246,11 +11121,6 @@
       <c r="R77" t="n">
         <v>0.08091804761743888</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12263,22 +11133,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12399,11 +11259,6 @@
       <c r="R78" t="n">
         <v>0.07761646880347157</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12416,22 +11271,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12552,11 +11397,6 @@
       <c r="R79" t="n">
         <v>0.09440438888701204</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12569,22 +11409,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12705,11 +11535,6 @@
       <c r="R80" t="n">
         <v>0.05785954947167881</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12722,22 +11547,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12858,11 +11673,6 @@
       <c r="R81" t="n">
         <v>0.1078907301565852</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12875,22 +11685,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13011,11 +11811,6 @@
       <c r="R82" t="n">
         <v>0.04092504718728501</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13028,22 +11823,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13164,11 +11949,6 @@
       <c r="R83" t="n">
         <v>0.2966995079306092</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13181,22 +11961,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13317,11 +12087,6 @@
       <c r="R84" t="n">
         <v>0.04186585286975134</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13334,22 +12099,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13470,11 +12225,6 @@
       <c r="R85" t="n">
         <v>0.3911038968176213</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13487,22 +12237,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13623,11 +12363,6 @@
       <c r="R86" t="n">
         <v>0.229851613206787</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13640,22 +12375,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13776,11 +12501,6 @@
       <c r="R87" t="n">
         <v>0.2163309300769759</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13793,22 +12513,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13929,11 +12639,6 @@
       <c r="R88" t="n">
         <v>0.09464478190867698</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13946,22 +12651,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14082,11 +12777,6 @@
       <c r="R89" t="n">
         <v>0.13520683129811</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14099,22 +12789,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14235,11 +12915,6 @@
       <c r="R90" t="n">
         <v>0.08112409877886599</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14252,22 +12927,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14388,11 +13053,6 @@
       <c r="R91" t="n">
         <v>0.13520683129811</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14405,22 +13065,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14541,11 +13191,6 @@
       <c r="R92" t="n">
         <v>0.108165465038488</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14558,22 +13203,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14694,11 +13329,6 @@
       <c r="R93" t="n">
         <v>0.13520683129811</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14711,22 +13341,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14847,11 +13467,6 @@
       <c r="R94" t="n">
         <v>0.2704136625962199</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14864,22 +13479,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15000,11 +13605,6 @@
       <c r="R95" t="n">
         <v>0.162248197557732</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15017,22 +13617,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15153,11 +13743,6 @@
       <c r="R96" t="n">
         <v>0.08112409877886599</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15170,22 +13755,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15306,11 +13881,6 @@
       <c r="R97" t="n">
         <v>0.09464478190867698</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15323,22 +13893,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>

--- a/diseases/d196/2020-2025.xlsx
+++ b/diseases/d196/2020-2025.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0.2670143014862483</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -909,6 +924,11 @@
       <c r="R3" t="n">
         <v>0.06675357537156208</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +941,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1047,6 +1077,11 @@
       <c r="R4" t="n">
         <v>0.05340286029724966</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1059,12 +1094,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1185,6 +1230,11 @@
       <c r="R5" t="n">
         <v>0.0801042904458745</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1247,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1323,6 +1383,11 @@
       <c r="R6" t="n">
         <v>1.415175797877116</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1335,12 +1400,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1461,6 +1536,11 @@
       <c r="R7" t="n">
         <v>0.4005214522293725</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1553,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1599,6 +1689,11 @@
       <c r="R8" t="n">
         <v>0.1735592959660614</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1611,12 +1706,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1737,6 +1842,11 @@
       <c r="R9" t="n">
         <v>0.04005214522293725</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1859,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1875,6 +1995,11 @@
       <c r="R10" t="n">
         <v>0.3337678768578104</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1887,12 +2012,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2013,6 +2148,11 @@
       <c r="R11" t="n">
         <v>0.1335071507431242</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2165,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2301,11 @@
       <c r="R12" t="n">
         <v>0.1335071507431242</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2318,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2454,11 @@
       <c r="R13" t="n">
         <v>0.1335071507431242</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2471,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2565,6 +2745,11 @@
       <c r="R15" t="n">
         <v>0.08016458858898501</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2762,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2841,6 +3036,11 @@
       <c r="R17" t="n">
         <v>0.1068861181186467</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2853,12 +3053,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3117,6 +3327,11 @@
       <c r="R19" t="n">
         <v>0.3473798838856016</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3129,12 +3344,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3393,6 +3618,11 @@
       <c r="R21" t="n">
         <v>0.09352535335381583</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3405,12 +3635,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3669,6 +3909,11 @@
       <c r="R23" t="n">
         <v>0.09352535335381583</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,12 +3926,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3945,6 +4200,11 @@
       <c r="R25" t="n">
         <v>0.240493765766955</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3957,12 +4217,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4221,6 +4491,11 @@
       <c r="R27" t="n">
         <v>0.3607406486504325</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4233,12 +4508,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4497,6 +4782,11 @@
       <c r="R29" t="n">
         <v>0.1336076476483083</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4509,12 +4799,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4773,6 +5073,11 @@
       <c r="R31" t="n">
         <v>0.2538545305317858</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4785,12 +5090,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5049,6 +5364,11 @@
       <c r="R33" t="n">
         <v>0.6279559439470491</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5061,12 +5381,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5325,6 +5655,11 @@
       <c r="R35" t="n">
         <v>0.2939368248262783</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5337,12 +5672,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5601,6 +5946,11 @@
       <c r="R37" t="n">
         <v>0.1068861181186467</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5613,12 +5963,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5739,6 +6099,11 @@
       <c r="R38" t="n">
         <v>0.0669710276637224</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5751,12 +6116,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5877,6 +6252,11 @@
       <c r="R39" t="n">
         <v>0.02678841106548896</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5889,12 +6269,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6015,6 +6405,11 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6027,12 +6422,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6153,6 +6558,11 @@
       <c r="R41" t="n">
         <v>0.04018261659823344</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6165,12 +6575,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6291,6 +6711,11 @@
       <c r="R42" t="n">
         <v>0.1875188774584227</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6303,12 +6728,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6429,6 +6864,11 @@
       <c r="R43" t="n">
         <v>0.1473362608601893</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6441,12 +6881,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6567,6 +7017,11 @@
       <c r="R44" t="n">
         <v>0.2277014940566562</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6579,12 +7034,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6705,6 +7170,11 @@
       <c r="R45" t="n">
         <v>0.2009130829911672</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6717,12 +7187,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6843,6 +7323,11 @@
       <c r="R46" t="n">
         <v>0.1741246719256782</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6855,12 +7340,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -6981,6 +7476,11 @@
       <c r="R47" t="n">
         <v>0.2277014940566562</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6993,12 +7493,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7119,6 +7629,11 @@
       <c r="R48" t="n">
         <v>0.1875188774584227</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7131,12 +7646,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7257,6 +7782,11 @@
       <c r="R49" t="n">
         <v>0.2946725217203786</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7269,12 +7799,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7395,6 +7935,11 @@
       <c r="R50" t="n">
         <v>0.5374368788783208</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7407,12 +7952,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7533,6 +8088,11 @@
       <c r="R51" t="n">
         <v>0.631488332682027</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7545,12 +8105,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7671,6 +8241,11 @@
       <c r="R52" t="n">
         <v>0.2821543614111184</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7683,12 +8258,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7809,6 +8394,11 @@
       <c r="R53" t="n">
         <v>0.1209232977476222</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7821,12 +8411,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7947,6 +8547,11 @@
       <c r="R54" t="n">
         <v>0.1209232977476222</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7959,12 +8564,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8085,6 +8700,11 @@
       <c r="R55" t="n">
         <v>0.3627698932428666</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8097,12 +8717,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8223,6 +8853,11 @@
       <c r="R56" t="n">
         <v>0.1881029076074123</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8235,12 +8870,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8361,6 +9006,11 @@
       <c r="R57" t="n">
         <v>0.3090262053550345</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8373,12 +9023,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8499,6 +9159,11 @@
       <c r="R58" t="n">
         <v>0.1209232977476222</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8511,12 +9176,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8637,6 +9312,11 @@
       <c r="R59" t="n">
         <v>0.1343592197195802</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8649,12 +9329,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8775,6 +9465,11 @@
       <c r="R60" t="n">
         <v>0.1746669856354543</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8787,12 +9482,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8913,6 +9618,11 @@
       <c r="R61" t="n">
         <v>0.1477951416915382</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8925,12 +9635,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9189,6 +9909,11 @@
       <c r="R63" t="n">
         <v>0.1888087777740241</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9201,12 +9926,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9465,6 +10200,11 @@
       <c r="R65" t="n">
         <v>0.3506448730089018</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9477,12 +10217,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9741,6 +10491,11 @@
       <c r="R67" t="n">
         <v>0.2022951190435972</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9753,12 +10508,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10017,6 +10782,11 @@
       <c r="R69" t="n">
         <v>0.06743170634786574</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10029,12 +10799,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10293,6 +11073,11 @@
       <c r="R71" t="n">
         <v>0.2022951190435972</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10305,12 +11090,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10569,6 +11364,11 @@
       <c r="R73" t="n">
         <v>0.7147760872873768</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10581,12 +11381,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10845,6 +11655,11 @@
       <c r="R75" t="n">
         <v>0.1348634126957315</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10857,12 +11672,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11121,6 +11946,11 @@
       <c r="R77" t="n">
         <v>0.08091804761743888</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11133,12 +11963,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11397,6 +12237,11 @@
       <c r="R79" t="n">
         <v>0.09440438888701204</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11409,12 +12254,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11673,6 +12528,11 @@
       <c r="R81" t="n">
         <v>0.1078907301565852</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11685,12 +12545,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11949,6 +12819,11 @@
       <c r="R83" t="n">
         <v>0.2966995079306092</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11961,12 +12836,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12225,6 +13110,11 @@
       <c r="R85" t="n">
         <v>0.3911038968176213</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12237,12 +13127,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12363,6 +13263,11 @@
       <c r="R86" t="n">
         <v>0.229851613206787</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12375,12 +13280,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12501,6 +13416,11 @@
       <c r="R87" t="n">
         <v>0.2163309300769759</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12513,12 +13433,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12639,6 +13569,11 @@
       <c r="R88" t="n">
         <v>0.09464478190867698</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12651,12 +13586,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -12777,6 +13722,11 @@
       <c r="R89" t="n">
         <v>0.13520683129811</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12789,12 +13739,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12915,6 +13875,11 @@
       <c r="R90" t="n">
         <v>0.08112409877886599</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12927,12 +13892,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13053,6 +14028,11 @@
       <c r="R91" t="n">
         <v>0.13520683129811</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13065,12 +14045,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13191,6 +14181,11 @@
       <c r="R92" t="n">
         <v>0.108165465038488</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13203,12 +14198,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13329,6 +14334,11 @@
       <c r="R93" t="n">
         <v>0.13520683129811</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13341,12 +14351,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13467,6 +14487,11 @@
       <c r="R94" t="n">
         <v>0.2704136625962199</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13479,12 +14504,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13605,6 +14640,11 @@
       <c r="R95" t="n">
         <v>0.162248197557732</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13617,12 +14657,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13743,6 +14793,11 @@
       <c r="R96" t="n">
         <v>0.08112409877886599</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13755,12 +14810,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -13881,6 +14946,11 @@
       <c r="R97" t="n">
         <v>0.09464478190867698</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13893,12 +14963,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>

--- a/diseases/d196/2020-2025.xlsx
+++ b/diseases/d196/2020-2025.xlsx
@@ -2607,6 +2607,11 @@
       <c r="R14" t="n">
         <v>0.0103132587174378</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2619,12 +2624,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2898,6 +2913,11 @@
       <c r="R16" t="n">
         <v>0.01125082769175033</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2910,12 +2930,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3189,6 +3219,11 @@
       <c r="R18" t="n">
         <v>0.008438120768812746</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3201,12 +3236,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3480,6 +3525,11 @@
       <c r="R20" t="n">
         <v>0.009375689743125274</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3492,12 +3542,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3771,6 +3831,11 @@
       <c r="R22" t="n">
         <v>0.01078204320459407</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3783,12 +3848,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4062,6 +4137,11 @@
       <c r="R24" t="n">
         <v>0.008438120768812746</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4074,12 +4154,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4353,6 +4443,11 @@
       <c r="R26" t="n">
         <v>0.01359475012753165</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4365,12 +4460,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4644,6 +4749,11 @@
       <c r="R28" t="n">
         <v>0.0375027589725011</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4656,12 +4766,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4935,6 +5055,11 @@
       <c r="R30" t="n">
         <v>0.04359695730553253</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4947,12 +5072,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5226,6 +5361,11 @@
       <c r="R32" t="n">
         <v>0.03703397448534483</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5238,12 +5378,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5517,6 +5667,11 @@
       <c r="R34" t="n">
         <v>0.03515883653671978</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5529,12 +5684,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5808,6 +5973,11 @@
       <c r="R36" t="n">
         <v>0.03047099166515714</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5820,12 +5990,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -9771,6 +9951,11 @@
       <c r="R62" t="n">
         <v>0.04751068696454927</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9783,12 +9968,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10062,6 +10257,11 @@
       <c r="R64" t="n">
         <v>0.04656988128208294</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10074,12 +10274,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10353,6 +10563,11 @@
       <c r="R66" t="n">
         <v>0.04374746423468398</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10365,12 +10580,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10644,6 +10869,11 @@
       <c r="R68" t="n">
         <v>0.03810263013988605</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10656,12 +10886,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10935,6 +11175,11 @@
       <c r="R70" t="n">
         <v>0.04045464434605185</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10947,12 +11192,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11226,6 +11481,11 @@
       <c r="R72" t="n">
         <v>0.04421786707591714</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11238,12 +11498,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11517,6 +11787,11 @@
       <c r="R74" t="n">
         <v>0.0639747864077099</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11529,12 +11804,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11808,6 +12093,11 @@
       <c r="R76" t="n">
         <v>0.08326130289826951</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11820,12 +12110,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12099,6 +12399,11 @@
       <c r="R78" t="n">
         <v>0.07761646880347157</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12111,12 +12416,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12390,6 +12705,11 @@
       <c r="R80" t="n">
         <v>0.05785954947167881</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12402,12 +12722,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12681,6 +13011,11 @@
       <c r="R82" t="n">
         <v>0.04092504718728501</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12693,12 +13028,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12972,6 +13317,11 @@
       <c r="R84" t="n">
         <v>0.04186585286975134</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12984,12 +13334,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
